--- a/Report/Demo_Bulk_Import_Classes_Roster.xlsx
+++ b/Report/Demo_Bulk_Import_Classes_Roster.xlsx
@@ -30,7 +30,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001E293B"/>
+      <color rgb="001F497D"/>
       <sz val="13"/>
     </font>
     <font>
@@ -41,10 +41,10 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="10"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -53,8 +53,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E293B"/>
-        <bgColor rgb="001E293B"/>
+        <fgColor rgb="00DCE6F1"/>
+        <bgColor rgb="00DCE6F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004F81BD"/>
+        <bgColor rgb="004F81BD"/>
       </patternFill>
     </fill>
   </fills>
@@ -68,38 +74,32 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </left>
       <right style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </right>
       <top style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -471,60 +471,60 @@
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
     <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="31" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DANH SÁCH LỚP HỌC (tạo mới)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1">
+          <t>CLASS LIST CREATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="25" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Mã lớp (ClassCode)*</t>
+          <t>ClassCode*</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Tên lớp (ClassName)*</t>
+          <t>ClassName*</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Mã khóa học (CourseCode)*</t>
+          <t>CourseCode*</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Ngày bắt đầu (dd/MM/yyyy)*</t>
+          <t>StartDate (dd/MM/yyyy)*</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ngày kết thúc (dd/MM/yyyy)*</t>
+          <t>EndDate (dd/MM/yyyy)*</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Địa điểm</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Sĩ số tối đa (Capacity)*</t>
+          <t>Capacity*</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Trạng thái (Status)*</t>
+          <t>Status*</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
           <t>A320-SIM-2026B</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>A320 Simulator Type Rating Batch 02</t>
         </is>
@@ -554,7 +554,7 @@
           <t>31/12/2026</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Sim Bay 02 - Hangar B</t>
         </is>
@@ -585,32 +585,32 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PHÂN CÔNG GIẢNG VIÊN THEO MÔN HỌC</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>Mã lớp (ClassCode)*</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>Mã môn học (SubjectCode)*</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>Username giảng viên*</t>
+          <t>INSTRUCTOR SUBJECT ASSIGNMENTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="25" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ClassCode*</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>SubjectCode*</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Instructor Username*</t>
         </is>
       </c>
     </row>
@@ -665,26 +665,26 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DANH SÁCH HỌC VIÊN XẾP LỚP</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>Mã lớp (ClassCode)*</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>Username học viên*</t>
+          <t>STUDENT CLASS ENROLLMENT ROSTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="25" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ClassCode*</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Student Username*</t>
         </is>
       </c>
     </row>

--- a/Report/Demo_Bulk_Import_Classes_Roster.xlsx
+++ b/Report/Demo_Bulk_Import_Classes_Roster.xlsx
@@ -546,12 +546,12 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>15/01/2027</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
